--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA392"/>
+  <dimension ref="A1:AA394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -41685,6 +41685,192 @@
         </is>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>Transan Interactive Distribution Srl</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>Transan Interactive Distribution Srl</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>22495</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>Intrarea Binelui Nr. 1a, Complex Fortuna, Sector 4</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>042159</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.transan.ro</t>
+        </is>
+      </c>
+      <c r="J393" s="2" t="inlineStr"/>
+      <c r="K393" s="2" t="inlineStr"/>
+      <c r="L393" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="M393" s="2" t="inlineStr"/>
+      <c r="N393" s="2" t="inlineStr">
+        <is>
+          <t>catalin.mohora@transan.ro</t>
+        </is>
+      </c>
+      <c r="O393" s="2" t="inlineStr"/>
+      <c r="P393" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q393" s="2" t="inlineStr">
+        <is>
+          <t>24483930</t>
+        </is>
+      </c>
+      <c r="R393" s="2" t="inlineStr"/>
+      <c r="S393" s="2" t="inlineStr"/>
+      <c r="T393" s="2" t="inlineStr"/>
+      <c r="U393" s="2" t="inlineStr"/>
+      <c r="V393" s="2" t="inlineStr"/>
+      <c r="W393" s="2" t="inlineStr">
+        <is>
+          <t>Catalin Marius</t>
+        </is>
+      </c>
+      <c r="X393" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y393" s="2" t="inlineStr"/>
+      <c r="Z393" s="2" t="inlineStr"/>
+      <c r="AA393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/catalin-marius-mohora-15078a93/</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>Transan Interactive Distribution Srl</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>Transan Interactive Distribution Srl</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>22495</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>Intrarea Binelui Nr. 1a, Complex Fortuna, Sector 4</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>042159</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.transan.ro</t>
+        </is>
+      </c>
+      <c r="J394" s="2" t="inlineStr"/>
+      <c r="K394" s="2" t="inlineStr"/>
+      <c r="L394" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="inlineStr"/>
+      <c r="N394" s="2" t="inlineStr">
+        <is>
+          <t>catalin.mohora@transan.ro</t>
+        </is>
+      </c>
+      <c r="O394" s="2" t="inlineStr"/>
+      <c r="P394" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q394" s="2" t="inlineStr">
+        <is>
+          <t>24483930</t>
+        </is>
+      </c>
+      <c r="R394" s="2" t="inlineStr"/>
+      <c r="S394" s="2" t="inlineStr"/>
+      <c r="T394" s="2" t="inlineStr"/>
+      <c r="U394" s="2" t="inlineStr"/>
+      <c r="V394" s="2" t="inlineStr"/>
+      <c r="W394" s="2" t="inlineStr">
+        <is>
+          <t>Marian Oprea</t>
+        </is>
+      </c>
+      <c r="X394" s="2" t="inlineStr">
+        <is>
+          <t>Sales Development Representative</t>
+        </is>
+      </c>
+      <c r="Y394" s="2" t="inlineStr"/>
+      <c r="Z394" s="2" t="inlineStr"/>
+      <c r="AA394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marian-oprea-62b74123/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA394"/>
+  <dimension ref="A1:AA398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -41871,6 +41871,402 @@
         </is>
       </c>
     </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>Wine Focus Intertrade Srl</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>Wine Focus Intertrade Srl</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>103071</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>216 Bulevardul Bucureștii Noi</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>012361</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>https://winefocus.ro</t>
+        </is>
+      </c>
+      <c r="J395" s="2" t="inlineStr"/>
+      <c r="K395" s="2" t="inlineStr"/>
+      <c r="L395" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M395" s="2" t="inlineStr"/>
+      <c r="N395" s="2" t="inlineStr">
+        <is>
+          <t>contact@winefocus.ro</t>
+        </is>
+      </c>
+      <c r="O395" s="2" t="inlineStr"/>
+      <c r="P395" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q395" s="2" t="inlineStr">
+        <is>
+          <t>44595733</t>
+        </is>
+      </c>
+      <c r="R395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine-focus-intertrade-srl/</t>
+        </is>
+      </c>
+      <c r="S395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winefocus.ro/</t>
+        </is>
+      </c>
+      <c r="T395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winefocus.ro/</t>
+        </is>
+      </c>
+      <c r="U395" s="2" t="inlineStr"/>
+      <c r="V395" s="2" t="inlineStr"/>
+      <c r="W395" s="2" t="inlineStr">
+        <is>
+          <t>Cosmin Udrea</t>
+        </is>
+      </c>
+      <c r="X395" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y395" s="2" t="inlineStr"/>
+      <c r="Z395" s="2" t="inlineStr"/>
+      <c r="AA395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cosmin-udrea-4847002/</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>Wine Focus Intertrade Srl</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>Wine Focus Intertrade Srl</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>103071</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>216 Bulevardul Bucureștii Noi</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>012361</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>https://winefocus.ro</t>
+        </is>
+      </c>
+      <c r="J396" s="2" t="inlineStr"/>
+      <c r="K396" s="2" t="inlineStr"/>
+      <c r="L396" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M396" s="2" t="inlineStr"/>
+      <c r="N396" s="2" t="inlineStr">
+        <is>
+          <t>contact@winefocus.ro</t>
+        </is>
+      </c>
+      <c r="O396" s="2" t="inlineStr"/>
+      <c r="P396" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q396" s="2" t="inlineStr">
+        <is>
+          <t>44595733</t>
+        </is>
+      </c>
+      <c r="R396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine-focus-intertrade-srl/</t>
+        </is>
+      </c>
+      <c r="S396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winefocus.ro/</t>
+        </is>
+      </c>
+      <c r="T396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winefocus.ro/</t>
+        </is>
+      </c>
+      <c r="U396" s="2" t="inlineStr"/>
+      <c r="V396" s="2" t="inlineStr"/>
+      <c r="W396" s="2" t="inlineStr">
+        <is>
+          <t>Robert Albu</t>
+        </is>
+      </c>
+      <c r="X396" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y396" s="2" t="inlineStr"/>
+      <c r="Z396" s="2" t="inlineStr"/>
+      <c r="AA396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robert-albu-ab9054100/</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>Transan Interactive Distribution Srl</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>Transan Interactive Distribution Srl</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>22495</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>Intrarea Binelui Nr. 1a, Complex Fortuna, Sector 4</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>042159</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.transan.ro</t>
+        </is>
+      </c>
+      <c r="J397" s="2" t="inlineStr"/>
+      <c r="K397" s="2" t="inlineStr"/>
+      <c r="L397" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="M397" s="2" t="inlineStr"/>
+      <c r="N397" s="2" t="inlineStr">
+        <is>
+          <t>catalin.mohora@transan.ro</t>
+        </is>
+      </c>
+      <c r="O397" s="2" t="inlineStr"/>
+      <c r="P397" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q397" s="2" t="inlineStr">
+        <is>
+          <t>24483930</t>
+        </is>
+      </c>
+      <c r="R397" s="2" t="inlineStr"/>
+      <c r="S397" s="2" t="inlineStr"/>
+      <c r="T397" s="2" t="inlineStr"/>
+      <c r="U397" s="2" t="inlineStr"/>
+      <c r="V397" s="2" t="inlineStr"/>
+      <c r="W397" s="2" t="inlineStr">
+        <is>
+          <t>Catalin Marius</t>
+        </is>
+      </c>
+      <c r="X397" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y397" s="2" t="inlineStr"/>
+      <c r="Z397" s="2" t="inlineStr"/>
+      <c r="AA397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/catalin-marius-mohora-15078a93/</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>Transan Interactive Distribution Srl</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>Transan Interactive Distribution Srl</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>22495</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>Intrarea Binelui Nr. 1a, Complex Fortuna, Sector 4</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>042159</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.transan.ro</t>
+        </is>
+      </c>
+      <c r="J398" s="2" t="inlineStr"/>
+      <c r="K398" s="2" t="inlineStr"/>
+      <c r="L398" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="M398" s="2" t="inlineStr"/>
+      <c r="N398" s="2" t="inlineStr">
+        <is>
+          <t>catalin.mohora@transan.ro</t>
+        </is>
+      </c>
+      <c r="O398" s="2" t="inlineStr"/>
+      <c r="P398" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q398" s="2" t="inlineStr">
+        <is>
+          <t>24483930</t>
+        </is>
+      </c>
+      <c r="R398" s="2" t="inlineStr"/>
+      <c r="S398" s="2" t="inlineStr"/>
+      <c r="T398" s="2" t="inlineStr"/>
+      <c r="U398" s="2" t="inlineStr"/>
+      <c r="V398" s="2" t="inlineStr"/>
+      <c r="W398" s="2" t="inlineStr">
+        <is>
+          <t>Marian Oprea</t>
+        </is>
+      </c>
+      <c r="X398" s="2" t="inlineStr">
+        <is>
+          <t>Sales Development Representative</t>
+        </is>
+      </c>
+      <c r="Y398" s="2" t="inlineStr"/>
+      <c r="Z398" s="2" t="inlineStr"/>
+      <c r="AA398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marian-oprea-62b74123/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA398"/>
+  <dimension ref="A1:AA403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -42267,6 +42267,487 @@
         </is>
       </c>
     </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>The Liquor Store Brașov</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>The Liquor Store Brașov</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>90097</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>Brasov</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>Brașov</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>34 Bulevardul 15 Noiembrie</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>500096</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>https://theliquor.store.ro</t>
+        </is>
+      </c>
+      <c r="J399" s="2" t="inlineStr"/>
+      <c r="K399" s="2" t="inlineStr"/>
+      <c r="L399" s="2" t="inlineStr"/>
+      <c r="M399" s="2" t="inlineStr"/>
+      <c r="N399" s="2" t="inlineStr">
+        <is>
+          <t>liquorstorebrasov@gmail.com</t>
+        </is>
+      </c>
+      <c r="O399" s="2" t="inlineStr"/>
+      <c r="P399" s="2" t="inlineStr"/>
+      <c r="Q399" s="2" t="inlineStr"/>
+      <c r="R399" s="2" t="inlineStr"/>
+      <c r="S399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Liquor-Store-Brasov-306669496354900/</t>
+        </is>
+      </c>
+      <c r="T399" s="2" t="inlineStr"/>
+      <c r="U399" s="2" t="inlineStr"/>
+      <c r="V399" s="2" t="inlineStr"/>
+      <c r="W399" s="2" t="inlineStr">
+        <is>
+          <t>Popovici Alexandru</t>
+        </is>
+      </c>
+      <c r="X399" s="2" t="inlineStr">
+        <is>
+          <t>Retail Sale</t>
+        </is>
+      </c>
+      <c r="Y399" s="2" t="inlineStr"/>
+      <c r="Z399" s="2" t="inlineStr"/>
+      <c r="AA399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/popovici-alexandru-3b1b851a4/?originalSubdomain=ro</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>Wine Focus Intertrade Srl</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>Wine Focus Intertrade Srl</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>103071</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>216 Bulevardul Bucureștii Noi</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>012361</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>https://winefocus.ro</t>
+        </is>
+      </c>
+      <c r="J400" s="2" t="inlineStr"/>
+      <c r="K400" s="2" t="inlineStr"/>
+      <c r="L400" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="inlineStr"/>
+      <c r="N400" s="2" t="inlineStr">
+        <is>
+          <t>contact@winefocus.ro</t>
+        </is>
+      </c>
+      <c r="O400" s="2" t="inlineStr"/>
+      <c r="P400" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q400" s="2" t="inlineStr">
+        <is>
+          <t>44595733</t>
+        </is>
+      </c>
+      <c r="R400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine-focus-intertrade-srl/</t>
+        </is>
+      </c>
+      <c r="S400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winefocus.ro/</t>
+        </is>
+      </c>
+      <c r="T400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winefocus.ro/</t>
+        </is>
+      </c>
+      <c r="U400" s="2" t="inlineStr"/>
+      <c r="V400" s="2" t="inlineStr"/>
+      <c r="W400" s="2" t="inlineStr">
+        <is>
+          <t>Cosmin Udrea</t>
+        </is>
+      </c>
+      <c r="X400" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y400" s="2" t="inlineStr"/>
+      <c r="Z400" s="2" t="inlineStr"/>
+      <c r="AA400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cosmin-udrea-4847002/</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>Wine Focus Intertrade Srl</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>Wine Focus Intertrade Srl</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>103071</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>216 Bulevardul Bucureștii Noi</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>012361</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>https://winefocus.ro</t>
+        </is>
+      </c>
+      <c r="J401" s="2" t="inlineStr"/>
+      <c r="K401" s="2" t="inlineStr"/>
+      <c r="L401" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M401" s="2" t="inlineStr"/>
+      <c r="N401" s="2" t="inlineStr">
+        <is>
+          <t>contact@winefocus.ro</t>
+        </is>
+      </c>
+      <c r="O401" s="2" t="inlineStr"/>
+      <c r="P401" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q401" s="2" t="inlineStr">
+        <is>
+          <t>44595733</t>
+        </is>
+      </c>
+      <c r="R401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine-focus-intertrade-srl/</t>
+        </is>
+      </c>
+      <c r="S401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winefocus.ro/</t>
+        </is>
+      </c>
+      <c r="T401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winefocus.ro/</t>
+        </is>
+      </c>
+      <c r="U401" s="2" t="inlineStr"/>
+      <c r="V401" s="2" t="inlineStr"/>
+      <c r="W401" s="2" t="inlineStr">
+        <is>
+          <t>Robert Albu</t>
+        </is>
+      </c>
+      <c r="X401" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y401" s="2" t="inlineStr"/>
+      <c r="Z401" s="2" t="inlineStr"/>
+      <c r="AA401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robert-albu-ab9054100/</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>Transan Interactive Distribution Srl</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>Transan Interactive Distribution Srl</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>22495</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>Intrarea Binelui Nr. 1a, Complex Fortuna, Sector 4</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>042159</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.transan.ro</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr"/>
+      <c r="K402" s="2" t="inlineStr"/>
+      <c r="L402" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="inlineStr"/>
+      <c r="N402" s="2" t="inlineStr">
+        <is>
+          <t>catalin.mohora@transan.ro</t>
+        </is>
+      </c>
+      <c r="O402" s="2" t="inlineStr"/>
+      <c r="P402" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q402" s="2" t="inlineStr">
+        <is>
+          <t>24483930</t>
+        </is>
+      </c>
+      <c r="R402" s="2" t="inlineStr"/>
+      <c r="S402" s="2" t="inlineStr"/>
+      <c r="T402" s="2" t="inlineStr"/>
+      <c r="U402" s="2" t="inlineStr"/>
+      <c r="V402" s="2" t="inlineStr"/>
+      <c r="W402" s="2" t="inlineStr">
+        <is>
+          <t>Catalin Marius</t>
+        </is>
+      </c>
+      <c r="X402" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y402" s="2" t="inlineStr"/>
+      <c r="Z402" s="2" t="inlineStr"/>
+      <c r="AA402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/catalin-marius-mohora-15078a93/</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>Transan Interactive Distribution Srl</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>Transan Interactive Distribution Srl</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>22495</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>Intrarea Binelui Nr. 1a, Complex Fortuna, Sector 4</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>042159</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.transan.ro</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr"/>
+      <c r="K403" s="2" t="inlineStr"/>
+      <c r="L403" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="M403" s="2" t="inlineStr"/>
+      <c r="N403" s="2" t="inlineStr">
+        <is>
+          <t>catalin.mohora@transan.ro</t>
+        </is>
+      </c>
+      <c r="O403" s="2" t="inlineStr"/>
+      <c r="P403" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q403" s="2" t="inlineStr">
+        <is>
+          <t>24483930</t>
+        </is>
+      </c>
+      <c r="R403" s="2" t="inlineStr"/>
+      <c r="S403" s="2" t="inlineStr"/>
+      <c r="T403" s="2" t="inlineStr"/>
+      <c r="U403" s="2" t="inlineStr"/>
+      <c r="V403" s="2" t="inlineStr"/>
+      <c r="W403" s="2" t="inlineStr">
+        <is>
+          <t>Marian Oprea</t>
+        </is>
+      </c>
+      <c r="X403" s="2" t="inlineStr">
+        <is>
+          <t>Sales Development Representative</t>
+        </is>
+      </c>
+      <c r="Y403" s="2" t="inlineStr"/>
+      <c r="Z403" s="2" t="inlineStr"/>
+      <c r="AA403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marian-oprea-62b74123/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
